--- a/input/12cut_hot_AB.xlsx
+++ b/input/12cut_hot_AB.xlsx
@@ -1804,6 +1804,36 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1811,30 +1841,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1843,11 +1849,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -1858,11 +1864,38 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
       <alignment horizontal="center" vertical="center"/>
@@ -1909,40 +1942,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="56">
@@ -1954,145 +1969,136 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="56">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
@@ -2101,73 +2107,67 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2631,7 +2631,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="343" t="inlineStr">
+      <c r="A1" s="325" t="inlineStr">
         <is>
           <t>12 граней горячая фиксация с эффектом АВ</t>
         </is>
@@ -2692,26 +2692,26 @@
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A3" s="303" t="inlineStr">
+      <c r="A3" s="310" t="inlineStr">
         <is>
           <t xml:space="preserve">TOPAZ AB </t>
         </is>
       </c>
-      <c r="B3" s="303" t="inlineStr">
+      <c r="B3" s="310" t="inlineStr">
         <is>
           <t>SS6</t>
         </is>
       </c>
-      <c r="C3" s="303" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D3" s="303" t="n">
+      <c r="C3" s="310" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D3" s="310" t="n">
         <v>221</v>
       </c>
-      <c r="E3" s="303" t="n">
+      <c r="E3" s="310" t="n">
         <v>2</v>
       </c>
-      <c r="F3" s="303" t="n"/>
+      <c r="F3" s="310" t="n"/>
       <c r="G3" s="243">
         <f>E3-F3</f>
         <v/>
@@ -2721,7 +2721,7 @@
           <t>12cut/Topaz AB/SS6/Hot/008+</t>
         </is>
       </c>
-      <c r="I3" s="362" t="inlineStr">
+      <c r="I3" s="365" t="inlineStr">
         <is>
           <t>008+</t>
         </is>
@@ -2729,21 +2729,21 @@
     </row>
     <row r="4" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A4" s="428" t="n"/>
-      <c r="B4" s="301" t="inlineStr">
+      <c r="B4" s="311" t="inlineStr">
         <is>
           <t>SS8</t>
         </is>
       </c>
-      <c r="C4" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D4" s="301" t="n">
+      <c r="C4" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D4" s="311" t="n">
         <v>259</v>
       </c>
-      <c r="E4" s="301" t="n">
+      <c r="E4" s="311" t="n">
         <v>2</v>
       </c>
-      <c r="F4" s="301" t="n"/>
+      <c r="F4" s="311" t="n"/>
       <c r="G4" s="245">
         <f>E4-F4</f>
         <v/>
@@ -2757,21 +2757,21 @@
     </row>
     <row r="5" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A5" s="428" t="n"/>
-      <c r="B5" s="301" t="inlineStr">
+      <c r="B5" s="311" t="inlineStr">
         <is>
           <t>SS10</t>
         </is>
       </c>
-      <c r="C5" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D5" s="301" t="n">
+      <c r="C5" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D5" s="311" t="n">
         <v>281</v>
       </c>
-      <c r="E5" s="301" t="n">
+      <c r="E5" s="311" t="n">
         <v>2</v>
       </c>
-      <c r="F5" s="301" t="n"/>
+      <c r="F5" s="311" t="n"/>
       <c r="G5" s="245">
         <f>E5-F5</f>
         <v/>
@@ -2785,21 +2785,21 @@
     </row>
     <row r="6" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A6" s="428" t="n"/>
-      <c r="B6" s="301" t="inlineStr">
+      <c r="B6" s="311" t="inlineStr">
         <is>
           <t>SS12</t>
         </is>
       </c>
-      <c r="C6" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D6" s="301" t="n">
+      <c r="C6" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D6" s="311" t="n">
         <v>391</v>
       </c>
-      <c r="E6" s="301" t="n">
+      <c r="E6" s="311" t="n">
         <v>2</v>
       </c>
-      <c r="F6" s="301" t="n">
+      <c r="F6" s="311" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="245">
@@ -2815,21 +2815,21 @@
     </row>
     <row r="7" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A7" s="428" t="n"/>
-      <c r="B7" s="301" t="inlineStr">
+      <c r="B7" s="311" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C7" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D7" s="301" t="n">
+      <c r="C7" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D7" s="311" t="n">
         <v>499</v>
       </c>
-      <c r="E7" s="301" t="n">
+      <c r="E7" s="311" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="301" t="n"/>
+      <c r="F7" s="311" t="n"/>
       <c r="G7" s="245">
         <f>E7-F7</f>
         <v/>
@@ -2843,21 +2843,21 @@
     </row>
     <row r="8" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A8" s="430" t="n"/>
-      <c r="B8" s="302" t="inlineStr">
+      <c r="B8" s="312" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C8" s="302" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D8" s="302" t="n">
+      <c r="C8" s="312" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D8" s="312" t="n">
         <v>803</v>
       </c>
-      <c r="E8" s="302" t="n">
+      <c r="E8" s="312" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="302" t="n"/>
+      <c r="F8" s="312" t="n"/>
       <c r="G8" s="246">
         <f>E8-F8</f>
         <v/>
@@ -2870,26 +2870,26 @@
       <c r="I8" s="431" t="n"/>
     </row>
     <row r="9" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A9" s="303" t="inlineStr">
+      <c r="A9" s="310" t="inlineStr">
         <is>
           <t xml:space="preserve">SAPPHIRE AB </t>
         </is>
       </c>
-      <c r="B9" s="303" t="inlineStr">
+      <c r="B9" s="310" t="inlineStr">
         <is>
           <t>SS6</t>
         </is>
       </c>
-      <c r="C9" s="303" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D9" s="303" t="n">
+      <c r="C9" s="310" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D9" s="310" t="n">
         <v>221</v>
       </c>
-      <c r="E9" s="303" t="n">
+      <c r="E9" s="310" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="303" t="n"/>
+      <c r="F9" s="310" t="n"/>
       <c r="G9" s="243">
         <f>E9-F9</f>
         <v/>
@@ -2899,7 +2899,7 @@
           <t>12cut/Sapphire AB/SS6/Hot/013+</t>
         </is>
       </c>
-      <c r="I9" s="362" t="inlineStr">
+      <c r="I9" s="365" t="inlineStr">
         <is>
           <t>013+</t>
         </is>
@@ -2907,21 +2907,21 @@
     </row>
     <row r="10" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A10" s="428" t="n"/>
-      <c r="B10" s="301" t="inlineStr">
+      <c r="B10" s="311" t="inlineStr">
         <is>
           <t>SS8</t>
         </is>
       </c>
-      <c r="C10" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D10" s="301" t="n">
+      <c r="C10" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D10" s="311" t="n">
         <v>259</v>
       </c>
-      <c r="E10" s="301" t="n">
+      <c r="E10" s="311" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="301" t="n">
+      <c r="F10" s="311" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="245">
@@ -2937,21 +2937,21 @@
     </row>
     <row r="11" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A11" s="428" t="n"/>
-      <c r="B11" s="301" t="inlineStr">
+      <c r="B11" s="311" t="inlineStr">
         <is>
           <t>SS10</t>
         </is>
       </c>
-      <c r="C11" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D11" s="301" t="n">
+      <c r="C11" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D11" s="311" t="n">
         <v>281</v>
       </c>
-      <c r="E11" s="301" t="n">
+      <c r="E11" s="311" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="301" t="n"/>
+      <c r="F11" s="311" t="n"/>
       <c r="G11" s="245">
         <f>E11-F11</f>
         <v/>
@@ -2965,21 +2965,21 @@
     </row>
     <row r="12" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A12" s="428" t="n"/>
-      <c r="B12" s="301" t="inlineStr">
+      <c r="B12" s="311" t="inlineStr">
         <is>
           <t>SS12</t>
         </is>
       </c>
-      <c r="C12" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D12" s="301" t="n">
+      <c r="C12" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D12" s="311" t="n">
         <v>391</v>
       </c>
-      <c r="E12" s="301" t="n">
+      <c r="E12" s="311" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="301" t="n"/>
+      <c r="F12" s="311" t="n"/>
       <c r="G12" s="245">
         <f>E12-F12</f>
         <v/>
@@ -2993,21 +2993,21 @@
     </row>
     <row r="13" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A13" s="428" t="n"/>
-      <c r="B13" s="301" t="inlineStr">
+      <c r="B13" s="311" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C13" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D13" s="301" t="n">
+      <c r="C13" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D13" s="311" t="n">
         <v>499</v>
       </c>
-      <c r="E13" s="301" t="n">
+      <c r="E13" s="311" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="301" t="n"/>
+      <c r="F13" s="311" t="n"/>
       <c r="G13" s="245">
         <f>E13-F13</f>
         <v/>
@@ -3021,21 +3021,21 @@
     </row>
     <row r="14" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A14" s="430" t="n"/>
-      <c r="B14" s="302" t="inlineStr">
+      <c r="B14" s="312" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C14" s="302" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D14" s="302" t="n">
+      <c r="C14" s="312" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D14" s="312" t="n">
         <v>803</v>
       </c>
-      <c r="E14" s="302" t="n">
+      <c r="E14" s="312" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="302" t="n"/>
+      <c r="F14" s="312" t="n"/>
       <c r="G14" s="246">
         <f>E14-F14</f>
         <v/>
@@ -3048,26 +3048,26 @@
       <c r="I14" s="431" t="n"/>
     </row>
     <row r="15" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A15" s="303" t="inlineStr">
+      <c r="A15" s="310" t="inlineStr">
         <is>
           <t xml:space="preserve">Indicolite AB </t>
         </is>
       </c>
-      <c r="B15" s="303" t="inlineStr">
+      <c r="B15" s="310" t="inlineStr">
         <is>
           <t>SS6</t>
         </is>
       </c>
-      <c r="C15" s="303" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D15" s="303" t="n">
+      <c r="C15" s="310" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D15" s="310" t="n">
         <v>221</v>
       </c>
-      <c r="E15" s="303" t="n">
+      <c r="E15" s="310" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="303" t="n"/>
+      <c r="F15" s="310" t="n"/>
       <c r="G15" s="243">
         <f>E15-F15</f>
         <v/>
@@ -3077,7 +3077,7 @@
           <t>12cut/Indicolite AB/SS6/Hot/014+</t>
         </is>
       </c>
-      <c r="I15" s="362" t="inlineStr">
+      <c r="I15" s="365" t="inlineStr">
         <is>
           <t>014+</t>
         </is>
@@ -3085,21 +3085,21 @@
     </row>
     <row r="16" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A16" s="428" t="n"/>
-      <c r="B16" s="301" t="inlineStr">
+      <c r="B16" s="311" t="inlineStr">
         <is>
           <t>SS8</t>
         </is>
       </c>
-      <c r="C16" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D16" s="301" t="n">
+      <c r="C16" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D16" s="311" t="n">
         <v>259</v>
       </c>
-      <c r="E16" s="301" t="n">
+      <c r="E16" s="311" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="301" t="n"/>
+      <c r="F16" s="311" t="n"/>
       <c r="G16" s="245">
         <f>E16-F16</f>
         <v/>
@@ -3113,21 +3113,21 @@
     </row>
     <row r="17" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A17" s="428" t="n"/>
-      <c r="B17" s="301" t="inlineStr">
+      <c r="B17" s="311" t="inlineStr">
         <is>
           <t>SS10</t>
         </is>
       </c>
-      <c r="C17" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D17" s="301" t="n">
+      <c r="C17" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D17" s="311" t="n">
         <v>281</v>
       </c>
-      <c r="E17" s="301" t="n">
+      <c r="E17" s="311" t="n">
         <v>2</v>
       </c>
-      <c r="F17" s="301" t="n">
+      <c r="F17" s="311" t="n">
         <v>2</v>
       </c>
       <c r="G17" s="245">
@@ -3143,21 +3143,21 @@
     </row>
     <row r="18" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A18" s="428" t="n"/>
-      <c r="B18" s="301" t="inlineStr">
+      <c r="B18" s="311" t="inlineStr">
         <is>
           <t>SS12</t>
         </is>
       </c>
-      <c r="C18" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D18" s="301" t="n">
+      <c r="C18" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D18" s="311" t="n">
         <v>391</v>
       </c>
-      <c r="E18" s="301" t="n">
+      <c r="E18" s="311" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="301" t="n">
+      <c r="F18" s="311" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="245">
@@ -3173,21 +3173,21 @@
     </row>
     <row r="19" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A19" s="428" t="n"/>
-      <c r="B19" s="301" t="inlineStr">
+      <c r="B19" s="311" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C19" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D19" s="301" t="n">
+      <c r="C19" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D19" s="311" t="n">
         <v>499</v>
       </c>
-      <c r="E19" s="301" t="n">
+      <c r="E19" s="311" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="301" t="n"/>
+      <c r="F19" s="311" t="n"/>
       <c r="G19" s="245">
         <f>E19-F19</f>
         <v/>
@@ -3201,21 +3201,21 @@
     </row>
     <row r="20" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A20" s="430" t="n"/>
-      <c r="B20" s="302" t="inlineStr">
+      <c r="B20" s="312" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C20" s="302" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D20" s="302" t="n">
+      <c r="C20" s="312" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D20" s="312" t="n">
         <v>803</v>
       </c>
-      <c r="E20" s="302" t="n">
+      <c r="E20" s="312" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="302" t="n"/>
+      <c r="F20" s="312" t="n"/>
       <c r="G20" s="246">
         <f>E20-F20</f>
         <v/>
@@ -3228,26 +3228,26 @@
       <c r="I20" s="431" t="n"/>
     </row>
     <row r="21" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A21" s="303" t="inlineStr">
+      <c r="A21" s="310" t="inlineStr">
         <is>
           <t xml:space="preserve">Lt. Peridot AB </t>
         </is>
       </c>
-      <c r="B21" s="303" t="inlineStr">
+      <c r="B21" s="310" t="inlineStr">
         <is>
           <t>SS6</t>
         </is>
       </c>
-      <c r="C21" s="303" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D21" s="303" t="n">
+      <c r="C21" s="310" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D21" s="310" t="n">
         <v>221</v>
       </c>
-      <c r="E21" s="303" t="n">
+      <c r="E21" s="310" t="n">
         <v>2</v>
       </c>
-      <c r="F21" s="303" t="n">
+      <c r="F21" s="310" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="243">
@@ -3259,7 +3259,7 @@
           <t>12cut/Lt. Peridot AB/SS6/Hot/024+</t>
         </is>
       </c>
-      <c r="I21" s="362" t="inlineStr">
+      <c r="I21" s="365" t="inlineStr">
         <is>
           <t>024+</t>
         </is>
@@ -3267,21 +3267,21 @@
     </row>
     <row r="22" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A22" s="428" t="n"/>
-      <c r="B22" s="301" t="inlineStr">
+      <c r="B22" s="311" t="inlineStr">
         <is>
           <t>SS8</t>
         </is>
       </c>
-      <c r="C22" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D22" s="301" t="n">
+      <c r="C22" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D22" s="311" t="n">
         <v>259</v>
       </c>
-      <c r="E22" s="301" t="n">
+      <c r="E22" s="311" t="n">
         <v>2</v>
       </c>
-      <c r="F22" s="301" t="n">
+      <c r="F22" s="311" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="245">
@@ -3297,21 +3297,21 @@
     </row>
     <row r="23" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A23" s="428" t="n"/>
-      <c r="B23" s="301" t="inlineStr">
+      <c r="B23" s="311" t="inlineStr">
         <is>
           <t>SS10</t>
         </is>
       </c>
-      <c r="C23" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D23" s="301" t="n">
+      <c r="C23" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D23" s="311" t="n">
         <v>281</v>
       </c>
-      <c r="E23" s="301" t="n">
+      <c r="E23" s="311" t="n">
         <v>2</v>
       </c>
-      <c r="F23" s="301" t="n"/>
+      <c r="F23" s="311" t="n"/>
       <c r="G23" s="245">
         <f>E23-F23</f>
         <v/>
@@ -3325,21 +3325,21 @@
     </row>
     <row r="24" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A24" s="428" t="n"/>
-      <c r="B24" s="301" t="inlineStr">
+      <c r="B24" s="311" t="inlineStr">
         <is>
           <t>SS12</t>
         </is>
       </c>
-      <c r="C24" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D24" s="301" t="n">
+      <c r="C24" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D24" s="311" t="n">
         <v>391</v>
       </c>
-      <c r="E24" s="301" t="n">
+      <c r="E24" s="311" t="n">
         <v>2</v>
       </c>
-      <c r="F24" s="301" t="n"/>
+      <c r="F24" s="311" t="n"/>
       <c r="G24" s="245">
         <f>E24-F24</f>
         <v/>
@@ -3353,21 +3353,21 @@
     </row>
     <row r="25" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A25" s="428" t="n"/>
-      <c r="B25" s="301" t="inlineStr">
+      <c r="B25" s="311" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C25" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D25" s="301" t="n">
+      <c r="C25" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D25" s="311" t="n">
         <v>499</v>
       </c>
-      <c r="E25" s="301" t="n">
+      <c r="E25" s="311" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="301" t="n"/>
+      <c r="F25" s="311" t="n"/>
       <c r="G25" s="245">
         <f>E25-F25</f>
         <v/>
@@ -3381,21 +3381,21 @@
     </row>
     <row r="26" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A26" s="428" t="n"/>
-      <c r="B26" s="301" t="inlineStr">
+      <c r="B26" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C26" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D26" s="301" t="n">
+      <c r="C26" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D26" s="311" t="n">
         <v>803</v>
       </c>
-      <c r="E26" s="301" t="n">
+      <c r="E26" s="311" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="301" t="n"/>
+      <c r="F26" s="311" t="n"/>
       <c r="G26" s="245">
         <f>E26-F26</f>
         <v/>
@@ -3409,21 +3409,21 @@
     </row>
     <row r="27" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A27" s="430" t="n"/>
-      <c r="B27" s="302" t="inlineStr">
+      <c r="B27" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C27" s="302" t="n">
+      <c r="C27" s="312" t="n">
         <v>288</v>
       </c>
-      <c r="D27" s="302" t="n">
+      <c r="D27" s="312" t="n">
         <v>471</v>
       </c>
-      <c r="E27" s="302" t="n">
+      <c r="E27" s="312" t="n">
         <v>1</v>
       </c>
-      <c r="F27" s="302" t="n"/>
+      <c r="F27" s="312" t="n"/>
       <c r="G27" s="246">
         <f>E27-F27</f>
         <v/>
@@ -3441,21 +3441,21 @@
           <t xml:space="preserve">Tanzanite AB </t>
         </is>
       </c>
-      <c r="B28" s="303" t="inlineStr">
+      <c r="B28" s="310" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C28" s="303" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D28" s="303" t="n">
+      <c r="C28" s="310" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D28" s="310" t="n">
         <v>453</v>
       </c>
-      <c r="E28" s="303" t="n">
+      <c r="E28" s="310" t="n">
         <v>5</v>
       </c>
-      <c r="F28" s="303" t="n">
+      <c r="F28" s="310" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="243">
@@ -3467,7 +3467,7 @@
           <t>12cut/Tanzanite AB/SS16/Hot/028+</t>
         </is>
       </c>
-      <c r="I28" s="362" t="inlineStr">
+      <c r="I28" s="365" t="inlineStr">
         <is>
           <t>028+</t>
         </is>
@@ -3475,18 +3475,18 @@
     </row>
     <row r="29">
       <c r="A29" s="428" t="n"/>
-      <c r="B29" s="301" t="inlineStr">
+      <c r="B29" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C29" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D29" s="301" t="n">
+      <c r="C29" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D29" s="311" t="n">
         <v>726</v>
       </c>
-      <c r="E29" s="301">
+      <c r="E29" s="311">
         <f>5+1</f>
         <v/>
       </c>
@@ -3506,18 +3506,18 @@
     </row>
     <row r="30" ht="15.75" customHeight="1" thickBot="1">
       <c r="A30" s="432" t="n"/>
-      <c r="B30" s="302" t="inlineStr">
+      <c r="B30" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C30" s="302" t="n">
+      <c r="C30" s="312" t="n">
         <v>288</v>
       </c>
-      <c r="D30" s="302" t="n">
+      <c r="D30" s="312" t="n">
         <v>424</v>
       </c>
-      <c r="E30" s="302" t="n">
+      <c r="E30" s="312" t="n">
         <v>5</v>
       </c>
       <c r="F30" s="33" t="n">
@@ -3540,21 +3540,21 @@
           <t>FUCHSIA AB</t>
         </is>
       </c>
-      <c r="B31" s="303" t="inlineStr">
+      <c r="B31" s="310" t="inlineStr">
         <is>
           <t>SS6</t>
         </is>
       </c>
-      <c r="C31" s="311" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D31" s="303" t="n">
+      <c r="C31" s="313" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D31" s="310" t="n">
         <v>369</v>
       </c>
-      <c r="E31" s="338" t="n">
+      <c r="E31" s="329" t="n">
         <v>50</v>
       </c>
-      <c r="F31" s="311">
+      <c r="F31" s="313">
         <f>1+1+1</f>
         <v/>
       </c>
@@ -3567,7 +3567,7 @@
           <t>12cut/Fuchsia Shimmer/SS6/Hot/062</t>
         </is>
       </c>
-      <c r="I31" s="369" t="inlineStr">
+      <c r="I31" s="366" t="inlineStr">
         <is>
           <t>062</t>
         </is>
@@ -3575,21 +3575,21 @@
     </row>
     <row r="32" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A32" s="428" t="n"/>
-      <c r="B32" s="301" t="inlineStr">
+      <c r="B32" s="311" t="inlineStr">
         <is>
           <t>SS10</t>
         </is>
       </c>
-      <c r="C32" s="312" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D32" s="301" t="n">
+      <c r="C32" s="314" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D32" s="311" t="n">
         <v>545</v>
       </c>
-      <c r="E32" s="336" t="n">
+      <c r="E32" s="330" t="n">
         <v>20</v>
       </c>
-      <c r="F32" s="312">
+      <c r="F32" s="314">
         <f>1+1+1+1</f>
         <v/>
       </c>
@@ -3606,21 +3606,21 @@
     </row>
     <row r="33" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A33" s="428" t="n"/>
-      <c r="B33" s="301" t="inlineStr">
+      <c r="B33" s="311" t="inlineStr">
         <is>
           <t>SS12</t>
         </is>
       </c>
-      <c r="C33" s="312" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D33" s="301" t="n">
+      <c r="C33" s="314" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D33" s="311" t="n">
         <v>749</v>
       </c>
-      <c r="E33" s="336" t="n">
+      <c r="E33" s="330" t="n">
         <v>30</v>
       </c>
-      <c r="F33" s="312">
+      <c r="F33" s="314">
         <f>1+1</f>
         <v/>
       </c>
@@ -3637,21 +3637,21 @@
     </row>
     <row r="34" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A34" s="432" t="n"/>
-      <c r="B34" s="302" t="inlineStr">
+      <c r="B34" s="312" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C34" s="313" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D34" s="302" t="n">
+      <c r="C34" s="315" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D34" s="312" t="n">
         <v>1513</v>
       </c>
-      <c r="E34" s="339" t="n">
+      <c r="E34" s="331" t="n">
         <v>30</v>
       </c>
-      <c r="F34" s="313">
+      <c r="F34" s="315">
         <f>1+1</f>
         <v/>
       </c>
@@ -3696,7 +3696,7 @@
           <t>12cut/PRFB/SS20/Hot/255</t>
         </is>
       </c>
-      <c r="I35" s="362" t="n">
+      <c r="I35" s="365" t="n">
         <v>255</v>
       </c>
     </row>
@@ -3706,18 +3706,18 @@
           <t>SEFFAF AB</t>
         </is>
       </c>
-      <c r="B36" s="303" t="inlineStr">
+      <c r="B36" s="310" t="inlineStr">
         <is>
           <t>SS3</t>
         </is>
       </c>
-      <c r="C36" s="311" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D36" s="303" t="n">
+      <c r="C36" s="313" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D36" s="310" t="n">
         <v>166</v>
       </c>
-      <c r="E36" s="311" t="n">
+      <c r="E36" s="313" t="n">
         <v>47</v>
       </c>
       <c r="F36" s="32" t="n"/>
@@ -3730,24 +3730,24 @@
           <t>12cut/Crystal TRA HFT/SS3/Hot/110</t>
         </is>
       </c>
-      <c r="I36" s="362" t="n">
+      <c r="I36" s="365" t="n">
         <v>110</v>
       </c>
     </row>
     <row r="37" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A37" s="432" t="n"/>
-      <c r="B37" s="302" t="inlineStr">
+      <c r="B37" s="312" t="inlineStr">
         <is>
           <t>SS4</t>
         </is>
       </c>
-      <c r="C37" s="302" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D37" s="302" t="n">
+      <c r="C37" s="312" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D37" s="312" t="n">
         <v>166</v>
       </c>
-      <c r="E37" s="302" t="n">
+      <c r="E37" s="312" t="n">
         <v>40</v>
       </c>
       <c r="F37" s="33" t="n"/>
@@ -3763,23 +3763,23 @@
       <c r="I37" s="431" t="n"/>
     </row>
     <row r="38" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A38" s="303" t="inlineStr">
+      <c r="A38" s="310" t="inlineStr">
         <is>
           <t>NEON WHITE AB</t>
         </is>
       </c>
-      <c r="B38" s="303" t="inlineStr">
+      <c r="B38" s="310" t="inlineStr">
         <is>
           <t>SS6</t>
         </is>
       </c>
-      <c r="C38" s="303" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D38" s="303" t="n">
+      <c r="C38" s="310" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D38" s="310" t="n">
         <v>319</v>
       </c>
-      <c r="E38" s="303" t="n">
+      <c r="E38" s="310" t="n">
         <v>20</v>
       </c>
       <c r="F38" s="32">
@@ -3795,7 +3795,7 @@
           <t>12cut/Neon White AB/SS6/Hot/067+</t>
         </is>
       </c>
-      <c r="I38" s="362" t="inlineStr">
+      <c r="I38" s="365" t="inlineStr">
         <is>
           <t>067+</t>
         </is>
@@ -3803,18 +3803,18 @@
     </row>
     <row r="39" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A39" s="428" t="n"/>
-      <c r="B39" s="301" t="inlineStr">
+      <c r="B39" s="311" t="inlineStr">
         <is>
           <t>SS8</t>
         </is>
       </c>
-      <c r="C39" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D39" s="301" t="n">
+      <c r="C39" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D39" s="311" t="n">
         <v>413</v>
       </c>
-      <c r="E39" s="301" t="n">
+      <c r="E39" s="311" t="n">
         <v>20</v>
       </c>
       <c r="F39" s="34" t="n"/>
@@ -3831,18 +3831,18 @@
     </row>
     <row r="40" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A40" s="428" t="n"/>
-      <c r="B40" s="301" t="inlineStr">
+      <c r="B40" s="311" t="inlineStr">
         <is>
           <t>SS10</t>
         </is>
       </c>
-      <c r="C40" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D40" s="301" t="n">
+      <c r="C40" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D40" s="311" t="n">
         <v>457</v>
       </c>
-      <c r="E40" s="301" t="n">
+      <c r="E40" s="311" t="n">
         <v>20</v>
       </c>
       <c r="F40" s="34" t="n">
@@ -3861,18 +3861,18 @@
     </row>
     <row r="41" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A41" s="428" t="n"/>
-      <c r="B41" s="301" t="inlineStr">
+      <c r="B41" s="311" t="inlineStr">
         <is>
           <t>SS12</t>
         </is>
       </c>
-      <c r="C41" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D41" s="301" t="n">
+      <c r="C41" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D41" s="311" t="n">
         <v>558</v>
       </c>
-      <c r="E41" s="301" t="n">
+      <c r="E41" s="311" t="n">
         <v>20</v>
       </c>
       <c r="F41" s="34" t="n"/>
@@ -3889,18 +3889,18 @@
     </row>
     <row r="42" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A42" s="428" t="n"/>
-      <c r="B42" s="301" t="inlineStr">
+      <c r="B42" s="311" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C42" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D42" s="301" t="n">
+      <c r="C42" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D42" s="311" t="n">
         <v>803</v>
       </c>
-      <c r="E42" s="301" t="n">
+      <c r="E42" s="311" t="n">
         <v>20</v>
       </c>
       <c r="F42" s="34" t="n"/>
@@ -3917,21 +3917,21 @@
     </row>
     <row r="43" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A43" s="428" t="n"/>
-      <c r="B43" s="301" t="inlineStr">
+      <c r="B43" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C43" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D43" s="301" t="n">
+      <c r="C43" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D43" s="311" t="n">
         <v>969</v>
       </c>
-      <c r="E43" s="301" t="n">
+      <c r="E43" s="311" t="n">
         <v>14</v>
       </c>
-      <c r="F43" s="301" t="n"/>
+      <c r="F43" s="311" t="n"/>
       <c r="G43" s="245">
         <f>E43-F43</f>
         <v/>
@@ -3945,21 +3945,21 @@
     </row>
     <row r="44" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A44" s="430" t="n"/>
-      <c r="B44" s="302" t="inlineStr">
+      <c r="B44" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C44" s="302" t="n">
+      <c r="C44" s="312" t="n">
         <v>288</v>
       </c>
-      <c r="D44" s="302" t="n">
+      <c r="D44" s="312" t="n">
         <v>773</v>
       </c>
-      <c r="E44" s="302" t="n">
+      <c r="E44" s="312" t="n">
         <v>19</v>
       </c>
-      <c r="F44" s="302" t="n"/>
+      <c r="F44" s="312" t="n"/>
       <c r="G44" s="246">
         <f>E44-F44</f>
         <v/>
@@ -3977,22 +3977,22 @@
           <t>NEON PINK AB</t>
         </is>
       </c>
-      <c r="B45" s="303" t="inlineStr">
+      <c r="B45" s="310" t="inlineStr">
         <is>
           <t>SS6</t>
         </is>
       </c>
-      <c r="C45" s="303" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D45" s="303" t="n">
+      <c r="C45" s="310" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D45" s="310" t="n">
         <v>319</v>
       </c>
-      <c r="E45" s="303">
+      <c r="E45" s="310">
         <f>10+20</f>
         <v/>
       </c>
-      <c r="F45" s="303">
+      <c r="F45" s="310">
         <f>1+1+1+2+2+1+5+2+1+1+1+1</f>
         <v/>
       </c>
@@ -4005,7 +4005,7 @@
           <t>12cut/Neon Pink AB/SS6/Hot/068+</t>
         </is>
       </c>
-      <c r="I45" s="362" t="inlineStr">
+      <c r="I45" s="365" t="inlineStr">
         <is>
           <t>068+</t>
         </is>
@@ -4013,21 +4013,21 @@
     </row>
     <row r="46" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A46" s="428" t="n"/>
-      <c r="B46" s="317" t="inlineStr">
+      <c r="B46" s="319" t="inlineStr">
         <is>
           <t>SS8</t>
         </is>
       </c>
-      <c r="C46" s="317" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D46" s="317" t="n">
+      <c r="C46" s="319" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D46" s="319" t="n">
         <v>400</v>
       </c>
-      <c r="E46" s="317" t="n">
+      <c r="E46" s="319" t="n">
         <v>10</v>
       </c>
-      <c r="F46" s="317" t="n"/>
+      <c r="F46" s="319" t="n"/>
       <c r="G46" s="244">
         <f>E46-F46</f>
         <v/>
@@ -4041,22 +4041,22 @@
     </row>
     <row r="47" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A47" s="428" t="n"/>
-      <c r="B47" s="301" t="inlineStr">
+      <c r="B47" s="311" t="inlineStr">
         <is>
           <t>SS10</t>
         </is>
       </c>
-      <c r="C47" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D47" s="301" t="n">
+      <c r="C47" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D47" s="311" t="n">
         <v>457</v>
       </c>
-      <c r="E47" s="301">
+      <c r="E47" s="311">
         <f>10+20</f>
         <v/>
       </c>
-      <c r="F47" s="301">
+      <c r="F47" s="311">
         <f>1+1+1+1+1+1+1+1+1</f>
         <v/>
       </c>
@@ -4073,21 +4073,21 @@
     </row>
     <row r="48" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A48" s="428" t="n"/>
-      <c r="B48" s="301" t="inlineStr">
+      <c r="B48" s="311" t="inlineStr">
         <is>
           <t>SS12</t>
         </is>
       </c>
-      <c r="C48" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D48" s="301" t="n">
+      <c r="C48" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D48" s="311" t="n">
         <v>601</v>
       </c>
-      <c r="E48" s="301" t="n">
+      <c r="E48" s="311" t="n">
         <v>10</v>
       </c>
-      <c r="F48" s="301" t="n"/>
+      <c r="F48" s="311" t="n"/>
       <c r="G48" s="245">
         <f>E48-F48</f>
         <v/>
@@ -4101,22 +4101,22 @@
     </row>
     <row r="49" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A49" s="428" t="n"/>
-      <c r="B49" s="301" t="inlineStr">
+      <c r="B49" s="311" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C49" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D49" s="301" t="n">
+      <c r="C49" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D49" s="311" t="n">
         <v>802</v>
       </c>
-      <c r="E49" s="301">
+      <c r="E49" s="311">
         <f>10+20</f>
         <v/>
       </c>
-      <c r="F49" s="301">
+      <c r="F49" s="311">
         <f>1+1+2+1+1+1+1+1+1+1</f>
         <v/>
       </c>
@@ -4133,22 +4133,22 @@
     </row>
     <row r="50" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A50" s="428" t="n"/>
-      <c r="B50" s="301" t="inlineStr">
+      <c r="B50" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C50" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D50" s="301" t="n">
+      <c r="C50" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D50" s="311" t="n">
         <v>1023</v>
       </c>
-      <c r="E50" s="301">
+      <c r="E50" s="311">
         <f>10+11</f>
         <v/>
       </c>
-      <c r="F50" s="301">
+      <c r="F50" s="311">
         <f>1+1+1+7+1+1+1</f>
         <v/>
       </c>
@@ -4165,21 +4165,21 @@
     </row>
     <row r="51" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A51" s="428" t="n"/>
-      <c r="B51" s="318" t="inlineStr">
+      <c r="B51" s="320" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C51" s="318" t="n">
+      <c r="C51" s="320" t="n">
         <v>288</v>
       </c>
-      <c r="D51" s="318" t="n">
+      <c r="D51" s="320" t="n">
         <v>773</v>
       </c>
-      <c r="E51" s="318" t="n">
+      <c r="E51" s="320" t="n">
         <v>20</v>
       </c>
-      <c r="F51" s="318">
+      <c r="F51" s="320">
         <f>1+1</f>
         <v/>
       </c>
@@ -4195,26 +4195,26 @@
       <c r="I51" s="431" t="n"/>
     </row>
     <row r="52" ht="15.75" customHeight="1" thickTop="1">
-      <c r="A52" s="303" t="inlineStr">
+      <c r="A52" s="310" t="inlineStr">
         <is>
           <t>NEON PURPLE AB</t>
         </is>
       </c>
-      <c r="B52" s="303" t="inlineStr">
+      <c r="B52" s="310" t="inlineStr">
         <is>
           <t>SS6</t>
         </is>
       </c>
-      <c r="C52" s="303" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D52" s="303" t="n">
+      <c r="C52" s="310" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D52" s="310" t="n">
         <v>319</v>
       </c>
-      <c r="E52" s="303" t="n">
+      <c r="E52" s="310" t="n">
         <v>10</v>
       </c>
-      <c r="F52" s="303" t="n"/>
+      <c r="F52" s="310" t="n"/>
       <c r="G52" s="243">
         <f>E52-F52</f>
         <v/>
@@ -4224,7 +4224,7 @@
           <t>12cut/Neon Purple AB/SS6/Hot/073+</t>
         </is>
       </c>
-      <c r="I52" s="364" t="inlineStr">
+      <c r="I52" s="367" t="inlineStr">
         <is>
           <t>073+</t>
         </is>
@@ -4232,22 +4232,22 @@
     </row>
     <row r="53">
       <c r="A53" s="428" t="n"/>
-      <c r="B53" s="317" t="inlineStr">
+      <c r="B53" s="319" t="inlineStr">
         <is>
           <t>SS8</t>
         </is>
       </c>
-      <c r="C53" s="317" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D53" s="317" t="n">
+      <c r="C53" s="319" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D53" s="319" t="n">
         <v>413</v>
       </c>
-      <c r="E53" s="317">
+      <c r="E53" s="319">
         <f>10+20</f>
         <v/>
       </c>
-      <c r="F53" s="317">
+      <c r="F53" s="319">
         <f>1+1+3+1+1</f>
         <v/>
       </c>
@@ -4264,22 +4264,22 @@
     </row>
     <row r="54">
       <c r="A54" s="428" t="n"/>
-      <c r="B54" s="301" t="inlineStr">
+      <c r="B54" s="311" t="inlineStr">
         <is>
           <t>SS10</t>
         </is>
       </c>
-      <c r="C54" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D54" s="301" t="n">
+      <c r="C54" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D54" s="311" t="n">
         <v>468</v>
       </c>
-      <c r="E54" s="301">
+      <c r="E54" s="311">
         <f>10+20</f>
         <v/>
       </c>
-      <c r="F54" s="301">
+      <c r="F54" s="311">
         <f>1+1+1+1</f>
         <v/>
       </c>
@@ -4296,22 +4296,22 @@
     </row>
     <row r="55">
       <c r="A55" s="428" t="n"/>
-      <c r="B55" s="301" t="inlineStr">
+      <c r="B55" s="311" t="inlineStr">
         <is>
           <t>SS12</t>
         </is>
       </c>
-      <c r="C55" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D55" s="301" t="n">
+      <c r="C55" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D55" s="311" t="n">
         <v>558</v>
       </c>
-      <c r="E55" s="301">
+      <c r="E55" s="311">
         <f>10+20</f>
         <v/>
       </c>
-      <c r="F55" s="301" t="n">
+      <c r="F55" s="311" t="n">
         <v>1</v>
       </c>
       <c r="G55" s="245">
@@ -4327,22 +4327,22 @@
     </row>
     <row r="56">
       <c r="A56" s="428" t="n"/>
-      <c r="B56" s="301" t="inlineStr">
+      <c r="B56" s="311" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C56" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D56" s="301" t="n">
+      <c r="C56" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D56" s="311" t="n">
         <v>803</v>
       </c>
-      <c r="E56" s="301">
+      <c r="E56" s="311">
         <f>10+20</f>
         <v/>
       </c>
-      <c r="F56" s="301">
+      <c r="F56" s="311">
         <f>1+1+1+1</f>
         <v/>
       </c>
@@ -4359,22 +4359,22 @@
     </row>
     <row r="57" ht="15.75" customHeight="1" thickBot="1">
       <c r="A57" s="430" t="n"/>
-      <c r="B57" s="302" t="inlineStr">
+      <c r="B57" s="312" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C57" s="302" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D57" s="302" t="n">
+      <c r="C57" s="312" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D57" s="312" t="n">
         <v>1023</v>
       </c>
-      <c r="E57" s="302">
+      <c r="E57" s="312">
         <f>10+11</f>
         <v/>
       </c>
-      <c r="F57" s="302">
+      <c r="F57" s="312">
         <f>1+1</f>
         <v/>
       </c>
@@ -4395,21 +4395,21 @@
           <t>NEON YELLOW AB</t>
         </is>
       </c>
-      <c r="B58" s="303" t="inlineStr">
+      <c r="B58" s="310" t="inlineStr">
         <is>
           <t>SS6</t>
         </is>
       </c>
-      <c r="C58" s="303" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D58" s="303" t="n">
+      <c r="C58" s="310" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D58" s="310" t="n">
         <v>319</v>
       </c>
-      <c r="E58" s="303" t="n">
+      <c r="E58" s="310" t="n">
         <v>20</v>
       </c>
-      <c r="F58" s="303">
+      <c r="F58" s="310">
         <f>1+1</f>
         <v/>
       </c>
@@ -4419,10 +4419,10 @@
       </c>
       <c r="H58" s="291" t="inlineStr">
         <is>
-          <t>12cut/Neon Yellow AB/SS3/Hot/069+</t>
-        </is>
-      </c>
-      <c r="I58" s="362" t="inlineStr">
+          <t>12cut/Neon Yellow AB/SS6/Hot/069+</t>
+        </is>
+      </c>
+      <c r="I58" s="365" t="inlineStr">
         <is>
           <t>069+</t>
         </is>
@@ -4430,133 +4430,133 @@
     </row>
     <row r="59" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A59" s="428" t="n"/>
-      <c r="B59" s="301" t="inlineStr">
+      <c r="B59" s="311" t="inlineStr">
         <is>
           <t>SS8</t>
         </is>
       </c>
-      <c r="C59" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D59" s="301" t="n">
+      <c r="C59" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D59" s="311" t="n">
         <v>413</v>
       </c>
-      <c r="E59" s="301" t="n">
+      <c r="E59" s="311" t="n">
         <v>20</v>
       </c>
-      <c r="F59" s="301" t="n"/>
+      <c r="F59" s="311" t="n"/>
       <c r="G59" s="245">
         <f>E59-F59</f>
         <v/>
       </c>
       <c r="H59" s="292" t="inlineStr">
         <is>
-          <t>12cut/Neon Yellow AB/SS3/Hot/069+</t>
+          <t>12cut/Neon Yellow AB/SS8/Hot/069+</t>
         </is>
       </c>
       <c r="I59" s="429" t="n"/>
     </row>
     <row r="60" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A60" s="428" t="n"/>
-      <c r="B60" s="301" t="inlineStr">
+      <c r="B60" s="311" t="inlineStr">
         <is>
           <t>SS10</t>
         </is>
       </c>
-      <c r="C60" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D60" s="301" t="n">
+      <c r="C60" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D60" s="311" t="n">
         <v>457</v>
       </c>
-      <c r="E60" s="301" t="n">
+      <c r="E60" s="311" t="n">
         <v>20</v>
       </c>
-      <c r="F60" s="301" t="n"/>
+      <c r="F60" s="311" t="n"/>
       <c r="G60" s="245">
         <f>E60-F60</f>
         <v/>
       </c>
       <c r="H60" s="292" t="inlineStr">
         <is>
-          <t>12cut/Neon Yellow AB/SS3/Hot/069+</t>
+          <t>12cut/Neon Yellow AB/SS10/Hot/069+</t>
         </is>
       </c>
       <c r="I60" s="429" t="n"/>
     </row>
     <row r="61" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A61" s="428" t="n"/>
-      <c r="B61" s="301" t="inlineStr">
+      <c r="B61" s="311" t="inlineStr">
         <is>
           <t>SS12</t>
         </is>
       </c>
-      <c r="C61" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D61" s="301" t="n">
+      <c r="C61" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D61" s="311" t="n">
         <v>558</v>
       </c>
-      <c r="E61" s="301" t="n">
+      <c r="E61" s="311" t="n">
         <v>20</v>
       </c>
-      <c r="F61" s="301" t="n"/>
+      <c r="F61" s="311" t="n"/>
       <c r="G61" s="245">
         <f>E61-F61</f>
         <v/>
       </c>
       <c r="H61" s="292" t="inlineStr">
         <is>
-          <t>12cut/Neon Yellow AB/SS3/Hot/069+</t>
+          <t>12cut/Neon Yellow AB/SS12/Hot/069+</t>
         </is>
       </c>
       <c r="I61" s="429" t="n"/>
     </row>
     <row r="62" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A62" s="428" t="n"/>
-      <c r="B62" s="336" t="inlineStr">
+      <c r="B62" s="330" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C62" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D62" s="301" t="n">
+      <c r="C62" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D62" s="311" t="n">
         <v>803</v>
       </c>
-      <c r="E62" s="301" t="n">
+      <c r="E62" s="311" t="n">
         <v>20</v>
       </c>
-      <c r="F62" s="301" t="n"/>
+      <c r="F62" s="311" t="n"/>
       <c r="G62" s="245">
         <f>E62-F62</f>
         <v/>
       </c>
       <c r="H62" s="292" t="inlineStr">
         <is>
-          <t>12cut/Neon Yellow AB/SS3/Hot/069+</t>
+          <t>12cut/Neon Yellow AB/SS16/Hot/069+</t>
         </is>
       </c>
       <c r="I62" s="429" t="n"/>
     </row>
     <row r="63" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A63" s="428" t="n"/>
-      <c r="B63" s="301" t="inlineStr">
+      <c r="B63" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C63" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D63" s="301" t="n">
+      <c r="C63" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D63" s="311" t="n">
         <v>1023</v>
       </c>
-      <c r="E63" s="301" t="n">
+      <c r="E63" s="311" t="n">
         <v>19</v>
       </c>
-      <c r="F63" s="301" t="n">
+      <c r="F63" s="311" t="n">
         <v>1</v>
       </c>
       <c r="G63" s="245">
@@ -4565,35 +4565,35 @@
       </c>
       <c r="H63" s="292" t="inlineStr">
         <is>
-          <t>12cut/Neon Yellow AB/SS3/Hot/069+</t>
+          <t>12cut/Neon Yellow AB/SS20/Hot/069+</t>
         </is>
       </c>
       <c r="I63" s="429" t="n"/>
     </row>
     <row r="64" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A64" s="432" t="n"/>
-      <c r="B64" s="302" t="inlineStr">
+      <c r="B64" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C64" s="302" t="n">
+      <c r="C64" s="312" t="n">
         <v>288</v>
       </c>
-      <c r="D64" s="302" t="n">
+      <c r="D64" s="312" t="n">
         <v>773</v>
       </c>
-      <c r="E64" s="302" t="n">
+      <c r="E64" s="312" t="n">
         <v>20</v>
       </c>
-      <c r="F64" s="302" t="n"/>
+      <c r="F64" s="312" t="n"/>
       <c r="G64" s="246">
         <f>E64-F64</f>
         <v/>
       </c>
       <c r="H64" s="295" t="inlineStr">
         <is>
-          <t>12cut/Neon Yellow AB/SS3/Hot/069+</t>
+          <t>12cut/Neon Yellow AB/SS30/Hot/069+</t>
         </is>
       </c>
       <c r="I64" s="431" t="n"/>
@@ -4604,21 +4604,21 @@
           <t>NEON BLUE AB</t>
         </is>
       </c>
-      <c r="B65" s="303" t="inlineStr">
+      <c r="B65" s="310" t="inlineStr">
         <is>
           <t>SS6</t>
         </is>
       </c>
-      <c r="C65" s="303" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D65" s="303" t="n">
+      <c r="C65" s="310" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D65" s="310" t="n">
         <v>319</v>
       </c>
-      <c r="E65" s="303" t="n">
+      <c r="E65" s="310" t="n">
         <v>20</v>
       </c>
-      <c r="F65" s="303">
+      <c r="F65" s="310">
         <f>1+1+1+1+1</f>
         <v/>
       </c>
@@ -4631,7 +4631,7 @@
           <t>12cut/Neon Blue AB/SS6/Hot/070+</t>
         </is>
       </c>
-      <c r="I65" s="362" t="inlineStr">
+      <c r="I65" s="365" t="inlineStr">
         <is>
           <t>070+</t>
         </is>
@@ -4639,22 +4639,22 @@
     </row>
     <row r="66" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A66" s="428" t="n"/>
-      <c r="B66" s="301" t="inlineStr">
+      <c r="B66" s="311" t="inlineStr">
         <is>
           <t>SS8</t>
         </is>
       </c>
-      <c r="C66" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D66" s="301" t="n">
+      <c r="C66" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D66" s="311" t="n">
         <v>413</v>
       </c>
-      <c r="E66" s="301">
+      <c r="E66" s="311">
         <f>20</f>
         <v/>
       </c>
-      <c r="F66" s="301">
+      <c r="F66" s="311">
         <f>1+1+1</f>
         <v/>
       </c>
@@ -4671,21 +4671,21 @@
     </row>
     <row r="67" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A67" s="428" t="n"/>
-      <c r="B67" s="301" t="inlineStr">
+      <c r="B67" s="311" t="inlineStr">
         <is>
           <t>SS10</t>
         </is>
       </c>
-      <c r="C67" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D67" s="301" t="n">
+      <c r="C67" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D67" s="311" t="n">
         <v>457</v>
       </c>
-      <c r="E67" s="301" t="n">
+      <c r="E67" s="311" t="n">
         <v>20</v>
       </c>
-      <c r="F67" s="301" t="n">
+      <c r="F67" s="311" t="n">
         <v>1</v>
       </c>
       <c r="G67" s="245">
@@ -4701,21 +4701,21 @@
     </row>
     <row r="68" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A68" s="428" t="n"/>
-      <c r="B68" s="301" t="inlineStr">
+      <c r="B68" s="311" t="inlineStr">
         <is>
           <t>SS12</t>
         </is>
       </c>
-      <c r="C68" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D68" s="301" t="n">
+      <c r="C68" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D68" s="311" t="n">
         <v>558</v>
       </c>
-      <c r="E68" s="301" t="n">
+      <c r="E68" s="311" t="n">
         <v>20</v>
       </c>
-      <c r="F68" s="301" t="n">
+      <c r="F68" s="311" t="n">
         <v>1</v>
       </c>
       <c r="G68" s="245">
@@ -4731,21 +4731,21 @@
     </row>
     <row r="69" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A69" s="428" t="n"/>
-      <c r="B69" s="301" t="inlineStr">
+      <c r="B69" s="311" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C69" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D69" s="301" t="n">
+      <c r="C69" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D69" s="311" t="n">
         <v>803</v>
       </c>
-      <c r="E69" s="301" t="n">
+      <c r="E69" s="311" t="n">
         <v>19</v>
       </c>
-      <c r="F69" s="301" t="n">
+      <c r="F69" s="311" t="n">
         <v>1</v>
       </c>
       <c r="G69" s="245">
@@ -4761,21 +4761,21 @@
     </row>
     <row r="70" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A70" s="428" t="n"/>
-      <c r="B70" s="301" t="inlineStr">
+      <c r="B70" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C70" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D70" s="301" t="n">
+      <c r="C70" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D70" s="311" t="n">
         <v>1023</v>
       </c>
-      <c r="E70" s="301" t="n">
+      <c r="E70" s="311" t="n">
         <v>19</v>
       </c>
-      <c r="F70" s="301">
+      <c r="F70" s="311">
         <f>1+1+1</f>
         <v/>
       </c>
@@ -4792,21 +4792,21 @@
     </row>
     <row r="71" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A71" s="432" t="n"/>
-      <c r="B71" s="302" t="inlineStr">
+      <c r="B71" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C71" s="302" t="n">
+      <c r="C71" s="312" t="n">
         <v>288</v>
       </c>
-      <c r="D71" s="302" t="n">
+      <c r="D71" s="312" t="n">
         <v>773</v>
       </c>
-      <c r="E71" s="302" t="n">
+      <c r="E71" s="312" t="n">
         <v>20</v>
       </c>
-      <c r="F71" s="302">
+      <c r="F71" s="312">
         <f>1+1</f>
         <v/>
       </c>
@@ -4822,26 +4822,26 @@
       <c r="I71" s="431" t="n"/>
     </row>
     <row r="72" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A72" s="303" t="inlineStr">
+      <c r="A72" s="310" t="inlineStr">
         <is>
           <t>NEON GREEN AB</t>
         </is>
       </c>
-      <c r="B72" s="303" t="inlineStr">
+      <c r="B72" s="310" t="inlineStr">
         <is>
           <t>SS6</t>
         </is>
       </c>
-      <c r="C72" s="303" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D72" s="303" t="n">
+      <c r="C72" s="310" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D72" s="310" t="n">
         <v>319</v>
       </c>
-      <c r="E72" s="303" t="n">
+      <c r="E72" s="310" t="n">
         <v>19</v>
       </c>
-      <c r="F72" s="303" t="n">
+      <c r="F72" s="310" t="n">
         <v>2</v>
       </c>
       <c r="G72" s="243">
@@ -4853,7 +4853,7 @@
           <t>12cut/Neon Green AB/SS6/Hot/071+</t>
         </is>
       </c>
-      <c r="I72" s="362" t="inlineStr">
+      <c r="I72" s="365" t="inlineStr">
         <is>
           <t>071+</t>
         </is>
@@ -4861,21 +4861,21 @@
     </row>
     <row r="73" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A73" s="428" t="n"/>
-      <c r="B73" s="301" t="inlineStr">
+      <c r="B73" s="311" t="inlineStr">
         <is>
           <t>SS8</t>
         </is>
       </c>
-      <c r="C73" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D73" s="317" t="n">
+      <c r="C73" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D73" s="319" t="n">
         <v>413</v>
       </c>
-      <c r="E73" s="317" t="n">
+      <c r="E73" s="319" t="n">
         <v>21</v>
       </c>
-      <c r="F73" s="317" t="n"/>
+      <c r="F73" s="319" t="n"/>
       <c r="G73" s="244">
         <f>E73-F73</f>
         <v/>
@@ -4889,21 +4889,21 @@
     </row>
     <row r="74" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A74" s="428" t="n"/>
-      <c r="B74" s="301" t="inlineStr">
+      <c r="B74" s="311" t="inlineStr">
         <is>
           <t>SS10</t>
         </is>
       </c>
-      <c r="C74" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D74" s="301" t="n">
+      <c r="C74" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D74" s="311" t="n">
         <v>457</v>
       </c>
-      <c r="E74" s="301" t="n">
+      <c r="E74" s="311" t="n">
         <v>20</v>
       </c>
-      <c r="F74" s="301" t="n"/>
+      <c r="F74" s="311" t="n"/>
       <c r="G74" s="245">
         <f>E74-F74</f>
         <v/>
@@ -4917,21 +4917,21 @@
     </row>
     <row r="75" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A75" s="428" t="n"/>
-      <c r="B75" s="301" t="inlineStr">
+      <c r="B75" s="311" t="inlineStr">
         <is>
           <t>SS12</t>
         </is>
       </c>
-      <c r="C75" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D75" s="301" t="n">
+      <c r="C75" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D75" s="311" t="n">
         <v>558</v>
       </c>
-      <c r="E75" s="301" t="n">
+      <c r="E75" s="311" t="n">
         <v>20</v>
       </c>
-      <c r="F75" s="301" t="n"/>
+      <c r="F75" s="311" t="n"/>
       <c r="G75" s="245">
         <f>E75-F75</f>
         <v/>
@@ -4945,21 +4945,21 @@
     </row>
     <row r="76" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A76" s="428" t="n"/>
-      <c r="B76" s="301" t="inlineStr">
+      <c r="B76" s="311" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C76" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D76" s="301" t="n">
+      <c r="C76" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D76" s="311" t="n">
         <v>803</v>
       </c>
-      <c r="E76" s="301" t="n">
+      <c r="E76" s="311" t="n">
         <v>20</v>
       </c>
-      <c r="F76" s="301" t="n"/>
+      <c r="F76" s="311" t="n"/>
       <c r="G76" s="245">
         <f>E76-F76</f>
         <v/>
@@ -4973,21 +4973,21 @@
     </row>
     <row r="77" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A77" s="428" t="n"/>
-      <c r="B77" s="301" t="inlineStr">
+      <c r="B77" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C77" s="301" t="n">
-        <v>1440</v>
-      </c>
-      <c r="D77" s="301" t="n">
+      <c r="C77" s="311" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D77" s="311" t="n">
         <v>1023</v>
       </c>
-      <c r="E77" s="301" t="n">
+      <c r="E77" s="311" t="n">
         <v>19</v>
       </c>
-      <c r="F77" s="301" t="n"/>
+      <c r="F77" s="311" t="n"/>
       <c r="G77" s="245">
         <f>E77-F77</f>
         <v/>
@@ -5001,22 +5001,22 @@
     </row>
     <row r="78" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A78" s="430" t="n"/>
-      <c r="B78" s="302" t="inlineStr">
+      <c r="B78" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C78" s="302" t="n">
+      <c r="C78" s="312" t="n">
         <v>288</v>
       </c>
-      <c r="D78" s="302" t="n">
+      <c r="D78" s="312" t="n">
         <v>773</v>
       </c>
-      <c r="E78" s="302">
+      <c r="E78" s="312">
         <f>10+10</f>
         <v/>
       </c>
-      <c r="F78" s="302" t="n"/>
+      <c r="F78" s="312" t="n"/>
       <c r="G78" s="246">
         <f>E78-F78</f>
         <v/>
@@ -5075,8 +5075,8 @@
     <mergeCell ref="A31:A34"/>
     <mergeCell ref="I31:I34"/>
     <mergeCell ref="A65:A71"/>
+    <mergeCell ref="I72:I78"/>
     <mergeCell ref="I28:I30"/>
-    <mergeCell ref="I72:I78"/>
   </mergeCells>
   <pageMargins left="0.7086614173228347" right="0.7086614173228347" top="0.7480314960629921" bottom="0.7480314960629921" header="0.3149606299212598" footer="0.3149606299212598"/>
   <pageSetup orientation="portrait" paperSize="9" scale="95" fitToHeight="2" verticalDpi="0"/>
